--- a/ptf_risk.xlsx
+++ b/ptf_risk.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="159">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -68,6 +68,60 @@
     <t xml:space="preserve">IT0001233417</t>
   </si>
   <si>
+    <t xml:space="preserve">ACEA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACE.MI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT0001207098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMPLIFON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMP.MI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT0004056880</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARCHR AVIATION RG-A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACHR.N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US03945R1023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARK Artificial Intelligence &amp; Robotics UCITS ETF Acc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARKI.MI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IE0003A512E4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARK Genomic Revolution UCITS ETF Acc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARKG.MI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IE000O5M6XO1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARK Innovation UCITS ETF Acc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARKK.MI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IE000GA3D489</t>
+  </si>
+  <si>
     <t xml:space="preserve">AVIO</t>
   </si>
   <si>
@@ -77,31 +131,58 @@
     <t xml:space="preserve">IT0005119810</t>
   </si>
   <si>
-    <t xml:space="preserve">BANCA IFIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IF.MI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT0003188064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BANCA MEDIOLANUM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BMED.MI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT0004776628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BRUNELLO CUCINELLI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BC.MI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT0004764699</t>
+    <t xml:space="preserve">AZIMUT HOLDING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AZM.MI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT0003261697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amundi MSCI Semiconductors UCITS ETF Acc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LSMC.FRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LU1900066033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BCO BPM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BAMI.MI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT0005218380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BIGBEAR.AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BBAI.N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US08975B1098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BREMBO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRE.MI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NL0015001KT6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BTP-1ST46 3,25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">508305.MOT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT0005083057</t>
   </si>
   <si>
     <t xml:space="preserve">BUZZI</t>
@@ -113,67 +194,76 @@
     <t xml:space="preserve">IT0001347308</t>
   </si>
   <si>
-    <t xml:space="preserve">CEMBRE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CMB.MI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT0001128047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CEMENTIR HOLD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CEM.MI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NL0013995087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CML.MI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT0005428971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EXPERT.AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EXAI.MI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT0004496029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GAROFALO H CARE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GHC.MI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT0005345233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GEFRAN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GE.MI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT0003203947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INTERPUMP GROUP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IP.MI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT0001078911</t>
+    <t xml:space="preserve">CALTAGIRONE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CALT.MI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT0003127930</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DANIELI &amp; C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DAN.MI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT0000076502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DATALOGIC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DAL.MI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT0004053440</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DATAVAULT AI INC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DVLT.O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US86633R6099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FINCANTIERI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FCT.MI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT0005599938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FINECOBANK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FBK.MI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT0000072170</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSBC Hang Seng Tech UCITS ETF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSTE.MI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IE00BMWXKN31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INTESA SANPAOLO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ISP.MI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT0000072618</t>
   </si>
   <si>
     <t xml:space="preserve">ITALGAS</t>
@@ -185,31 +275,103 @@
     <t xml:space="preserve">IT0005211237</t>
   </si>
   <si>
-    <t xml:space="preserve">MONCLER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MONC.MI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT0004965148</t>
+    <t xml:space="preserve">Invesco Physical Gold ETC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SGLD.MI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IE00B579F325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JAI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOBY.N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KYG651631007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KEYSIGHT TECHNOL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KEYS.N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US49338L1035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LU-VE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUVE.MI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT0005107492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAIRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAIRE.MI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT0004931058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORTHROP GRUMMAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC.N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US6668071029</t>
   </si>
   <si>
     <t xml:space="preserve">NOVO NORDISK -B-</t>
   </si>
   <si>
-    <t xml:space="preserve">NOV.DE</t>
+    <t xml:space="preserve">NOV.FRA</t>
   </si>
   <si>
     <t xml:space="preserve">DK0062498333</t>
   </si>
   <si>
-    <t xml:space="preserve">RAI WAY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RWAY.MI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT0005054967</t>
+    <t xml:space="preserve">OVS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OVS.MI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT0005043507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLC.MI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT0005339160</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRYSMIAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRY.MI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT0004176001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SNAM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRG.MI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT0003153415</t>
   </si>
   <si>
     <t xml:space="preserve">STMICROELECTRONICS</t>
@@ -221,31 +383,119 @@
     <t xml:space="preserve">NL0000226223</t>
   </si>
   <si>
-    <t xml:space="preserve">TENARIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TEN.MI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LU2598331598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TERNA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TRN.MI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT0003242622</t>
+    <t xml:space="preserve">TECHNOGYM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TGYM.MI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT0005162406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TELEDYNE TECH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TDY.N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US8793601050</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VanEck Crypto and Blockchain Innovators UCITS ETF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DAVV.FRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IE00BMDKNW35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VanEck R. Earth and Str. M. UCITS ETF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REMX.MI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IE0002PG6CA6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VanEck Uranium and Nuclear Technologies UCITS ETF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NUCL.MI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IE000M7V94E1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vanguard FTSE All-World UCITS ETF (USD) Acc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VWCE.FRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IE00BK5BQT80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WEBUILD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WBD.MI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT0003865570</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iShares Core MSCI World UCITS ETF USD (Acc)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SWDA.MI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IE00B4L5Y983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iShares Growth Portfolio UCITS ETF EUR (Acc)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAGR.FRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IE00BLLZQ805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iShares MSCI China UCITS ETF USD (Acc)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICGA.FRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IE00BJ5JPG56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iShares MSCI EMU Large Cap UCITS ETF EUR (Acc)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EMUL.MI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IE00BCLWRF22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iShares MSCI Japan EUR Hedged UCITS ETF (Acc)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IJPE.AS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IE00B42Z5J44</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="mm/dd/yyyy"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -282,7 +532,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -631,40 +881,30 @@
         <v>1.01651</v>
       </c>
       <c r="D2" t="n">
-        <v>-2000</v>
+        <v>200</v>
       </c>
       <c r="E2" t="n">
-        <v>2.166</v>
+        <v>2.69375</v>
       </c>
       <c r="F2" t="s">
         <v>17</v>
       </c>
       <c r="G2" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>45660</v>
-      </c>
-      <c r="I2" t="n">
-        <v>34128</v>
-      </c>
+        <v>45968</v>
+      </c>
+      <c r="I2"/>
       <c r="J2" s="1" t="n">
-        <v>45671</v>
-      </c>
-      <c r="K2" t="n">
-        <v>35124.58984375</v>
-      </c>
-      <c r="L2" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.0000634669479606188</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.0000629188841729135</v>
-      </c>
+        <v>46041</v>
+      </c>
+      <c r="K2"/>
+      <c r="L2"/>
+      <c r="M2"/>
+      <c r="N2"/>
       <c r="O2" t="n">
-        <v>2.26</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="3">
@@ -675,13 +915,13 @@
         <v>19</v>
       </c>
       <c r="C3" t="n">
-        <v>0.53446</v>
+        <v>0.79</v>
       </c>
       <c r="D3" t="n">
-        <v>140</v>
+        <v>70</v>
       </c>
       <c r="E3" t="n">
-        <v>14.21214</v>
+        <v>22.80252</v>
       </c>
       <c r="F3" t="s">
         <v>20</v>
@@ -690,28 +930,18 @@
         <v>1</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>45660</v>
-      </c>
-      <c r="I3" t="n">
-        <v>34128</v>
-      </c>
+        <v>46036</v>
+      </c>
+      <c r="I3"/>
       <c r="J3" s="1" t="n">
-        <v>45671</v>
-      </c>
-      <c r="K3" t="n">
-        <v>35124.58984375</v>
-      </c>
-      <c r="L3" t="n">
-        <v>14.72</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.000416436357243319</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.000419079626708275</v>
-      </c>
+        <v>46041</v>
+      </c>
+      <c r="K3"/>
+      <c r="L3"/>
+      <c r="M3"/>
+      <c r="N3"/>
       <c r="O3" t="n">
-        <v>11.6</v>
+        <v>19.01</v>
       </c>
     </row>
     <row r="4">
@@ -722,13 +952,13 @@
         <v>22</v>
       </c>
       <c r="C4" t="n">
-        <v>1.25501</v>
+        <v>0.57594</v>
       </c>
       <c r="D4" t="n">
-        <v>132</v>
+        <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>22.36242</v>
+        <v>14.295</v>
       </c>
       <c r="F4" t="s">
         <v>23</v>
@@ -737,28 +967,18 @@
         <v>1</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>45670</v>
-      </c>
-      <c r="I4" t="n">
-        <v>34799</v>
-      </c>
+        <v>46029</v>
+      </c>
+      <c r="I4"/>
       <c r="J4" s="1" t="n">
-        <v>45671</v>
-      </c>
-      <c r="K4" t="n">
-        <v>35124.58984375</v>
-      </c>
-      <c r="L4" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.000642616741860398</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.000649117900064447</v>
-      </c>
+        <v>46041</v>
+      </c>
+      <c r="K4"/>
+      <c r="L4"/>
+      <c r="M4"/>
+      <c r="N4"/>
       <c r="O4" t="n">
-        <v>18.33</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="5">
@@ -768,14 +988,12 @@
       <c r="B5" t="s">
         <v>25</v>
       </c>
-      <c r="C5" t="n">
-        <v>1.30179</v>
-      </c>
+      <c r="C5"/>
       <c r="D5" t="n">
-        <v>243</v>
+        <v>50</v>
       </c>
       <c r="E5" t="n">
-        <v>12.20312</v>
+        <v>9.66227901490401</v>
       </c>
       <c r="F5" t="s">
         <v>26</v>
@@ -784,29 +1002,21 @@
         <v>1</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>45666</v>
+        <v>45965</v>
       </c>
       <c r="I5" t="n">
-        <v>35316</v>
+        <v>43262</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>45671</v>
-      </c>
-      <c r="K5" t="n">
-        <v>35124.58984375</v>
-      </c>
-      <c r="L5" t="n">
-        <v>12.17</v>
-      </c>
+        <v>46041</v>
+      </c>
+      <c r="K5"/>
+      <c r="L5"/>
       <c r="M5" t="n">
-        <v>0.000345540831351229</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.000346480914201067</v>
-      </c>
-      <c r="O5" t="n">
-        <v>10.74</v>
-      </c>
+        <v>0.000223343327051547</v>
+      </c>
+      <c r="N5"/>
+      <c r="O5"/>
     </row>
     <row r="6">
       <c r="A6" t="s">
@@ -815,14 +1025,12 @@
       <c r="B6" t="s">
         <v>28</v>
       </c>
-      <c r="C6" t="n">
-        <v>0.82334</v>
-      </c>
+      <c r="C6"/>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>85</v>
       </c>
       <c r="E6" t="n">
-        <v>105.2228</v>
+        <v>8.573</v>
       </c>
       <c r="F6" t="s">
         <v>29</v>
@@ -831,29 +1039,17 @@
         <v>1</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>45649</v>
-      </c>
-      <c r="I6" t="n">
-        <v>33740</v>
-      </c>
+        <v>46041</v>
+      </c>
+      <c r="I6"/>
       <c r="J6" s="1" t="n">
-        <v>45671</v>
-      </c>
-      <c r="K6" t="n">
-        <v>35124.58984375</v>
-      </c>
-      <c r="L6" t="n">
-        <v>111.6</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0.00311863663307647</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0.00317726130031545</v>
-      </c>
-      <c r="O6" t="n">
-        <v>86.3</v>
-      </c>
+        <v>46041</v>
+      </c>
+      <c r="K6"/>
+      <c r="L6"/>
+      <c r="M6"/>
+      <c r="N6"/>
+      <c r="O6"/>
     </row>
     <row r="7">
       <c r="A7" t="s">
@@ -862,14 +1058,12 @@
       <c r="B7" t="s">
         <v>31</v>
       </c>
-      <c r="C7" t="n">
-        <v>0.89408</v>
-      </c>
+      <c r="C7"/>
       <c r="D7" t="n">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="E7" t="n">
-        <v>35.868</v>
+        <v>4.774</v>
       </c>
       <c r="F7" t="s">
         <v>32</v>
@@ -878,29 +1072,17 @@
         <v>1</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>45663</v>
-      </c>
-      <c r="I7" t="n">
-        <v>34781</v>
-      </c>
+        <v>46041</v>
+      </c>
+      <c r="I7"/>
       <c r="J7" s="1" t="n">
-        <v>45671</v>
-      </c>
-      <c r="K7" t="n">
-        <v>35124.58984375</v>
-      </c>
-      <c r="L7" t="n">
-        <v>35.64</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0.00103125269543716</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0.00101467377010074</v>
-      </c>
-      <c r="O7" t="n">
-        <v>31.6</v>
-      </c>
+        <v>46041</v>
+      </c>
+      <c r="K7"/>
+      <c r="L7"/>
+      <c r="M7"/>
+      <c r="N7"/>
+      <c r="O7"/>
     </row>
     <row r="8">
       <c r="A8" t="s">
@@ -909,14 +1091,12 @@
       <c r="B8" t="s">
         <v>34</v>
       </c>
-      <c r="C8" t="n">
-        <v>0.88215</v>
-      </c>
+      <c r="C8"/>
       <c r="D8" t="n">
-        <v>35</v>
+        <v>110</v>
       </c>
       <c r="E8" t="n">
-        <v>42.23014</v>
+        <v>7.077</v>
       </c>
       <c r="F8" t="s">
         <v>35</v>
@@ -925,29 +1105,17 @@
         <v>1</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>45663</v>
-      </c>
-      <c r="I8" t="n">
-        <v>34781</v>
-      </c>
+        <v>46041</v>
+      </c>
+      <c r="I8"/>
       <c r="J8" s="1" t="n">
-        <v>45671</v>
-      </c>
-      <c r="K8" t="n">
-        <v>35124.58984375</v>
-      </c>
-      <c r="L8" t="n">
-        <v>40.2</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0.00121417268048647</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0.00114449735011363</v>
-      </c>
-      <c r="O8" t="n">
-        <v>34.8</v>
-      </c>
+        <v>46041</v>
+      </c>
+      <c r="K8"/>
+      <c r="L8"/>
+      <c r="M8"/>
+      <c r="N8"/>
+      <c r="O8"/>
     </row>
     <row r="9">
       <c r="A9" t="s">
@@ -957,13 +1125,13 @@
         <v>37</v>
       </c>
       <c r="C9" t="n">
-        <v>1.05083</v>
+        <v>0.53446</v>
       </c>
       <c r="D9" t="n">
-        <v>213</v>
+        <v>20</v>
       </c>
       <c r="E9" t="n">
-        <v>10.84056</v>
+        <v>31.9975</v>
       </c>
       <c r="F9" t="s">
         <v>38</v>
@@ -972,28 +1140,18 @@
         <v>1</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>45665</v>
-      </c>
-      <c r="I9" t="n">
-        <v>35109</v>
-      </c>
+        <v>46027</v>
+      </c>
+      <c r="I9"/>
       <c r="J9" s="1" t="n">
-        <v>45671</v>
-      </c>
-      <c r="K9" t="n">
-        <v>35124.58984375</v>
-      </c>
-      <c r="L9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0.00030876869178843</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0.00029893587502968</v>
-      </c>
+        <v>46041</v>
+      </c>
+      <c r="K9"/>
+      <c r="L9"/>
+      <c r="M9"/>
+      <c r="N9"/>
       <c r="O9" t="n">
-        <v>9.16</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="10">
@@ -1004,13 +1162,13 @@
         <v>40</v>
       </c>
       <c r="C10" t="n">
-        <v>0.38962</v>
+        <v>1.13596</v>
       </c>
       <c r="D10" t="n">
-        <v>500</v>
+        <v>20</v>
       </c>
       <c r="E10" t="n">
-        <v>4.96942</v>
+        <v>34.14</v>
       </c>
       <c r="F10" t="s">
         <v>41</v>
@@ -1019,28 +1177,18 @@
         <v>1</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>45660</v>
-      </c>
-      <c r="I10" t="n">
-        <v>34128</v>
-      </c>
+        <v>45968</v>
+      </c>
+      <c r="I10"/>
       <c r="J10" s="1" t="n">
-        <v>45671</v>
-      </c>
-      <c r="K10" t="n">
-        <v>35124.58984375</v>
-      </c>
-      <c r="L10" t="n">
-        <v>4.92</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0.000145611228316925</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0.000140072810013907</v>
-      </c>
+        <v>46041</v>
+      </c>
+      <c r="K10"/>
+      <c r="L10"/>
+      <c r="M10"/>
+      <c r="N10"/>
       <c r="O10" t="n">
-        <v>2.9</v>
+        <v>19.28</v>
       </c>
     </row>
     <row r="11">
@@ -1050,14 +1198,12 @@
       <c r="B11" t="s">
         <v>43</v>
       </c>
-      <c r="C11" t="n">
-        <v>1.25808</v>
-      </c>
+      <c r="C11"/>
       <c r="D11" t="n">
-        <v>1346</v>
+        <v>15</v>
       </c>
       <c r="E11" t="n">
-        <v>1.31248</v>
+        <v>70.84</v>
       </c>
       <c r="F11" t="s">
         <v>44</v>
@@ -1066,29 +1212,17 @@
         <v>1</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>45666</v>
-      </c>
-      <c r="I11" t="n">
-        <v>35316</v>
-      </c>
+        <v>46041</v>
+      </c>
+      <c r="I11"/>
       <c r="J11" s="1" t="n">
-        <v>45671</v>
-      </c>
-      <c r="K11" t="n">
-        <v>35124.58984375</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0.0000371638917204666</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0.0000355876041701999</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.23</v>
-      </c>
+        <v>46041</v>
+      </c>
+      <c r="K11"/>
+      <c r="L11"/>
+      <c r="M11"/>
+      <c r="N11"/>
+      <c r="O11"/>
     </row>
     <row r="12">
       <c r="A12" t="s">
@@ -1097,14 +1231,12 @@
       <c r="B12" t="s">
         <v>46</v>
       </c>
-      <c r="C12" t="n">
-        <v>0.4292</v>
-      </c>
+      <c r="C12"/>
       <c r="D12" t="n">
-        <v>170</v>
+        <v>80</v>
       </c>
       <c r="E12" t="n">
-        <v>5.39735</v>
+        <v>12.83875</v>
       </c>
       <c r="F12" t="s">
         <v>47</v>
@@ -1113,28 +1245,18 @@
         <v>1</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>45660</v>
-      </c>
-      <c r="I12" t="n">
-        <v>34128</v>
-      </c>
+        <v>46010</v>
+      </c>
+      <c r="I12"/>
       <c r="J12" s="1" t="n">
-        <v>45671</v>
-      </c>
-      <c r="K12" t="n">
-        <v>35124.58984375</v>
-      </c>
-      <c r="L12" t="n">
-        <v>4.98</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0.000158150199249883</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0.000141781015014077</v>
-      </c>
+        <v>46041</v>
+      </c>
+      <c r="K12"/>
+      <c r="L12"/>
+      <c r="M12"/>
+      <c r="N12"/>
       <c r="O12" t="n">
-        <v>4.8</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="13">
@@ -1144,14 +1266,12 @@
       <c r="B13" t="s">
         <v>49</v>
       </c>
-      <c r="C13" t="n">
-        <v>1.18133</v>
-      </c>
+      <c r="C13"/>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="E13" t="n">
-        <v>9.2695</v>
+        <v>6.24400307534283</v>
       </c>
       <c r="F13" t="s">
         <v>50</v>
@@ -1160,29 +1280,21 @@
         <v>1</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>45649</v>
+        <v>45933</v>
       </c>
       <c r="I13" t="n">
-        <v>33740</v>
+        <v>43258</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>45671</v>
-      </c>
-      <c r="K13" t="n">
-        <v>35124.58984375</v>
-      </c>
-      <c r="L13" t="n">
-        <v>9.12</v>
-      </c>
+        <v>46041</v>
+      </c>
+      <c r="K13"/>
+      <c r="L13"/>
       <c r="M13" t="n">
-        <v>0.00027473325429757</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0.000259647160025779</v>
-      </c>
-      <c r="O13" t="n">
-        <v>7.74</v>
-      </c>
+        <v>0.000144343313961414</v>
+      </c>
+      <c r="N13"/>
+      <c r="O13"/>
     </row>
     <row r="14">
       <c r="A14" t="s">
@@ -1192,43 +1304,33 @@
         <v>52</v>
       </c>
       <c r="C14" t="n">
-        <v>0.94955</v>
+        <v>1.04082</v>
       </c>
       <c r="D14" t="n">
-        <v>-88</v>
+        <v>100</v>
       </c>
       <c r="E14" t="n">
-        <v>42.02</v>
+        <v>9.8495</v>
       </c>
       <c r="F14" t="s">
         <v>53</v>
       </c>
       <c r="G14" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>45670</v>
-      </c>
-      <c r="I14" t="n">
-        <v>34799</v>
-      </c>
+        <v>46036</v>
+      </c>
+      <c r="I14"/>
       <c r="J14" s="1" t="n">
-        <v>45671</v>
-      </c>
-      <c r="K14" t="n">
-        <v>35124.58984375</v>
-      </c>
-      <c r="L14" t="n">
-        <v>42.52</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0.00120750596281502</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0.00121054794345352</v>
-      </c>
+        <v>46041</v>
+      </c>
+      <c r="K14"/>
+      <c r="L14"/>
+      <c r="M14"/>
+      <c r="N14"/>
       <c r="O14" t="n">
-        <v>46.16</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="15">
@@ -1238,45 +1340,31 @@
       <c r="B15" t="s">
         <v>55</v>
       </c>
-      <c r="C15" t="n">
-        <v>0.55095</v>
-      </c>
+      <c r="C15"/>
       <c r="D15" t="n">
-        <v>-350</v>
+        <v>4000</v>
       </c>
       <c r="E15" t="n">
-        <v>5.41</v>
+        <v>88.06</v>
       </c>
       <c r="F15" t="s">
         <v>56</v>
       </c>
       <c r="G15" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>45644</v>
-      </c>
-      <c r="I15" t="n">
-        <v>34401</v>
-      </c>
+        <v>46041</v>
+      </c>
+      <c r="I15"/>
       <c r="J15" s="1" t="n">
-        <v>45671</v>
-      </c>
-      <c r="K15" t="n">
-        <v>35124.58984375</v>
-      </c>
-      <c r="L15" t="n">
-        <v>5.37</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0.000157262870265399</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0.000152884347515179</v>
-      </c>
-      <c r="O15" t="n">
-        <v>5.91</v>
-      </c>
+        <v>46041</v>
+      </c>
+      <c r="K15"/>
+      <c r="L15"/>
+      <c r="M15"/>
+      <c r="N15"/>
+      <c r="O15"/>
     </row>
     <row r="16">
       <c r="A16" t="s">
@@ -1286,43 +1374,33 @@
         <v>58</v>
       </c>
       <c r="C16" t="n">
-        <v>0.78057</v>
+        <v>0.89408</v>
       </c>
       <c r="D16" t="n">
-        <v>-62</v>
+        <v>24</v>
       </c>
       <c r="E16" t="n">
-        <v>49.65</v>
+        <v>50.47083</v>
       </c>
       <c r="F16" t="s">
         <v>59</v>
       </c>
       <c r="G16" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>45667</v>
-      </c>
-      <c r="I16" t="n">
-        <v>35090</v>
-      </c>
+        <v>46036</v>
+      </c>
+      <c r="I16"/>
       <c r="J16" s="1" t="n">
-        <v>45671</v>
-      </c>
-      <c r="K16" t="n">
-        <v>35124.58984375</v>
-      </c>
-      <c r="L16" t="n">
-        <v>53.32</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0.00141493302935309</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0.00151802484348405</v>
-      </c>
+        <v>46041</v>
+      </c>
+      <c r="K16"/>
+      <c r="L16"/>
+      <c r="M16"/>
+      <c r="N16"/>
       <c r="O16" t="n">
-        <v>59.8</v>
+        <v>40.2</v>
       </c>
     </row>
     <row r="17">
@@ -1332,12 +1410,14 @@
       <c r="B17" t="s">
         <v>61</v>
       </c>
-      <c r="C17"/>
+      <c r="C17" t="n">
+        <v>0.81526</v>
+      </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>75</v>
       </c>
       <c r="E17" t="n">
-        <v>127.45434</v>
+        <v>8.812</v>
       </c>
       <c r="F17" t="s">
         <v>62</v>
@@ -1346,28 +1426,22 @@
         <v>1</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>45518</v>
+        <v>45940</v>
       </c>
       <c r="I17" t="n">
-        <v>32328</v>
+        <v>42048</v>
       </c>
       <c r="J17" s="1" t="n">
-        <v>45671</v>
-      </c>
-      <c r="K17" t="n">
-        <v>35124.58984375</v>
-      </c>
-      <c r="L17" t="n">
-        <v>78.99</v>
-      </c>
+        <v>46041</v>
+      </c>
+      <c r="K17"/>
+      <c r="L17"/>
       <c r="M17" t="n">
-        <v>0.00394253711952487</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0.00224885188272327</v>
-      </c>
+        <v>0.0002095700152207</v>
+      </c>
+      <c r="N17"/>
       <c r="O17" t="n">
-        <v>71.62</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="18">
@@ -1378,13 +1452,13 @@
         <v>64</v>
       </c>
       <c r="C18" t="n">
-        <v>0.33855</v>
+        <v>0.94609</v>
       </c>
       <c r="D18" t="n">
-        <v>150</v>
+        <v>18</v>
       </c>
       <c r="E18" t="n">
-        <v>5.53966</v>
+        <v>52.74722</v>
       </c>
       <c r="F18" t="s">
         <v>65</v>
@@ -1393,28 +1467,18 @@
         <v>1</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>45660</v>
-      </c>
-      <c r="I18" t="n">
-        <v>34128</v>
-      </c>
+        <v>46036</v>
+      </c>
+      <c r="I18"/>
       <c r="J18" s="1" t="n">
-        <v>45671</v>
-      </c>
-      <c r="K18" t="n">
-        <v>35124.58984375</v>
-      </c>
-      <c r="L18" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0.000162320089076418</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0.000150891441681648</v>
-      </c>
+        <v>46041</v>
+      </c>
+      <c r="K18"/>
+      <c r="L18"/>
+      <c r="M18"/>
+      <c r="N18"/>
       <c r="O18" t="n">
-        <v>4.95</v>
+        <v>23.45</v>
       </c>
     </row>
     <row r="19">
@@ -1425,43 +1489,33 @@
         <v>67</v>
       </c>
       <c r="C19" t="n">
-        <v>1.22345</v>
+        <v>1.27769</v>
       </c>
       <c r="D19" t="n">
-        <v>89</v>
+        <v>-700</v>
       </c>
       <c r="E19" t="n">
-        <v>43.52217</v>
+        <v>4.439557</v>
       </c>
       <c r="F19" t="s">
         <v>68</v>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>45384</v>
-      </c>
-      <c r="I19" t="n">
-        <v>34325</v>
-      </c>
+        <v>46038</v>
+      </c>
+      <c r="I19"/>
       <c r="J19" s="1" t="n">
-        <v>45671</v>
-      </c>
-      <c r="K19" t="n">
-        <v>35124.58984375</v>
-      </c>
-      <c r="L19" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0.00126794377276038</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0.000669046958399759</v>
-      </c>
+        <v>46041</v>
+      </c>
+      <c r="K19"/>
+      <c r="L19"/>
+      <c r="M19"/>
+      <c r="N19"/>
       <c r="O19" t="n">
-        <v>22.64</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="20">
@@ -1471,14 +1525,12 @@
       <c r="B20" t="s">
         <v>70</v>
       </c>
-      <c r="C20" t="n">
-        <v>1.54079</v>
-      </c>
+      <c r="C20"/>
       <c r="D20" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E20" t="n">
-        <v>17.984</v>
+        <v>2.41598932323117</v>
       </c>
       <c r="F20" t="s">
         <v>71</v>
@@ -1487,29 +1539,21 @@
         <v>1</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>45670</v>
+        <v>45965</v>
       </c>
       <c r="I20" t="n">
-        <v>34799</v>
+        <v>43262</v>
       </c>
       <c r="J20" s="1" t="n">
-        <v>45671</v>
-      </c>
-      <c r="K20" t="n">
-        <v>35124.58984375</v>
-      </c>
-      <c r="L20" t="n">
-        <v>18.92</v>
-      </c>
+        <v>46041</v>
+      </c>
+      <c r="K20"/>
+      <c r="L20"/>
       <c r="M20" t="n">
-        <v>0.000516796459668381</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0.000538653976720146</v>
-      </c>
-      <c r="O20" t="n">
-        <v>12.05</v>
-      </c>
+        <v>0.0000558455301010395</v>
+      </c>
+      <c r="N20"/>
+      <c r="O20"/>
     </row>
     <row r="21">
       <c r="A21" t="s">
@@ -1519,13 +1563,13 @@
         <v>73</v>
       </c>
       <c r="C21" t="n">
-        <v>0.39032</v>
+        <v>1.18338</v>
       </c>
       <c r="D21" t="n">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="E21" t="n">
-        <v>7.72263</v>
+        <v>19.03833</v>
       </c>
       <c r="F21" t="s">
         <v>74</v>
@@ -1534,29 +1578,1011 @@
         <v>1</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>45660</v>
-      </c>
-      <c r="I21" t="n">
-        <v>34128</v>
-      </c>
+        <v>46031</v>
+      </c>
+      <c r="I21"/>
       <c r="J21" s="1" t="n">
-        <v>45671</v>
-      </c>
-      <c r="K21" t="n">
-        <v>35124.58984375</v>
-      </c>
-      <c r="L21" t="n">
-        <v>7.61</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0.000226284282700422</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0.000216657334188177</v>
-      </c>
+        <v>46041</v>
+      </c>
+      <c r="K21"/>
+      <c r="L21"/>
+      <c r="M21"/>
+      <c r="N21"/>
       <c r="O21" t="n">
-        <v>7.46</v>
-      </c>
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>75</v>
+      </c>
+      <c r="B22" t="s">
+        <v>76</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.75139</v>
+      </c>
+      <c r="D22" t="n">
+        <v>20</v>
+      </c>
+      <c r="E22" t="n">
+        <v>22.4575</v>
+      </c>
+      <c r="F22" t="s">
+        <v>77</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="1" t="n">
+        <v>46031</v>
+      </c>
+      <c r="I22"/>
+      <c r="J22" s="1" t="n">
+        <v>46041</v>
+      </c>
+      <c r="K22"/>
+      <c r="L22"/>
+      <c r="M22"/>
+      <c r="N22"/>
+      <c r="O22" t="n">
+        <v>17.55</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>78</v>
+      </c>
+      <c r="B23" t="s">
+        <v>79</v>
+      </c>
+      <c r="C23"/>
+      <c r="D23" t="n">
+        <v>236</v>
+      </c>
+      <c r="E23" t="n">
+        <v>6.78835</v>
+      </c>
+      <c r="F23" t="s">
+        <v>80</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" s="1" t="n">
+        <v>46041</v>
+      </c>
+      <c r="I23"/>
+      <c r="J23" s="1" t="n">
+        <v>46041</v>
+      </c>
+      <c r="K23"/>
+      <c r="L23"/>
+      <c r="M23"/>
+      <c r="N23"/>
+      <c r="O23"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>81</v>
+      </c>
+      <c r="B24" t="s">
+        <v>82</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1.37004</v>
+      </c>
+      <c r="D24" t="n">
+        <v>270</v>
+      </c>
+      <c r="E24" t="n">
+        <v>5.977</v>
+      </c>
+      <c r="F24" t="s">
+        <v>83</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" s="1" t="n">
+        <v>46036</v>
+      </c>
+      <c r="I24"/>
+      <c r="J24" s="1" t="n">
+        <v>46041</v>
+      </c>
+      <c r="K24"/>
+      <c r="L24"/>
+      <c r="M24"/>
+      <c r="N24"/>
+      <c r="O24" t="n">
+        <v>3.66</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>84</v>
+      </c>
+      <c r="B25" t="s">
+        <v>85</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.55095</v>
+      </c>
+      <c r="D25" t="n">
+        <v>120</v>
+      </c>
+      <c r="E25" t="n">
+        <v>9.39302</v>
+      </c>
+      <c r="F25" t="s">
+        <v>86</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="1" t="n">
+        <v>46027</v>
+      </c>
+      <c r="I25"/>
+      <c r="J25" s="1" t="n">
+        <v>46041</v>
+      </c>
+      <c r="K25"/>
+      <c r="L25"/>
+      <c r="M25"/>
+      <c r="N25"/>
+      <c r="O25" t="n">
+        <v>5.28</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>87</v>
+      </c>
+      <c r="B26" t="s">
+        <v>88</v>
+      </c>
+      <c r="C26"/>
+      <c r="D26" t="n">
+        <v>14</v>
+      </c>
+      <c r="E26" t="n">
+        <v>324.75789</v>
+      </c>
+      <c r="F26" t="s">
+        <v>89</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" s="1" t="n">
+        <v>46041</v>
+      </c>
+      <c r="I26"/>
+      <c r="J26" s="1" t="n">
+        <v>46041</v>
+      </c>
+      <c r="K26"/>
+      <c r="L26"/>
+      <c r="M26"/>
+      <c r="N26"/>
+      <c r="O26"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>90</v>
+      </c>
+      <c r="B27" t="s">
+        <v>91</v>
+      </c>
+      <c r="C27"/>
+      <c r="D27" t="n">
+        <v>30</v>
+      </c>
+      <c r="E27" t="n">
+        <v>14.9675888531649</v>
+      </c>
+      <c r="F27" t="s">
+        <v>92</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" s="1" t="n">
+        <v>45965</v>
+      </c>
+      <c r="I27" t="n">
+        <v>43262</v>
+      </c>
+      <c r="J27" s="1" t="n">
+        <v>46041</v>
+      </c>
+      <c r="K27"/>
+      <c r="L27"/>
+      <c r="M27" t="n">
+        <v>0.000345975425388676</v>
+      </c>
+      <c r="N27"/>
+      <c r="O27"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>93</v>
+      </c>
+      <c r="B28" t="s">
+        <v>94</v>
+      </c>
+      <c r="C28"/>
+      <c r="D28" t="n">
+        <v>3</v>
+      </c>
+      <c r="E28" t="n">
+        <v>173.778654392174</v>
+      </c>
+      <c r="F28" t="s">
+        <v>95</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" s="1" t="n">
+        <v>45994</v>
+      </c>
+      <c r="I28"/>
+      <c r="J28" s="1" t="n">
+        <v>46041</v>
+      </c>
+      <c r="K28"/>
+      <c r="L28"/>
+      <c r="M28"/>
+      <c r="N28"/>
+      <c r="O28"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>96</v>
+      </c>
+      <c r="B29" t="s">
+        <v>97</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.66144</v>
+      </c>
+      <c r="D29" t="n">
+        <v>20</v>
+      </c>
+      <c r="E29" t="n">
+        <v>39.6975</v>
+      </c>
+      <c r="F29" t="s">
+        <v>98</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" s="1" t="n">
+        <v>46029</v>
+      </c>
+      <c r="I29"/>
+      <c r="J29" s="1" t="n">
+        <v>46041</v>
+      </c>
+      <c r="K29"/>
+      <c r="L29"/>
+      <c r="M29"/>
+      <c r="N29"/>
+      <c r="O29" t="n">
+        <v>23.15</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>99</v>
+      </c>
+      <c r="B30" t="s">
+        <v>100</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1.54738</v>
+      </c>
+      <c r="D30" t="n">
+        <v>35</v>
+      </c>
+      <c r="E30" t="n">
+        <v>13.03428</v>
+      </c>
+      <c r="F30" t="s">
+        <v>101</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" s="1" t="n">
+        <v>45945</v>
+      </c>
+      <c r="I30" t="n">
+        <v>41907</v>
+      </c>
+      <c r="J30" s="1" t="n">
+        <v>46041</v>
+      </c>
+      <c r="K30"/>
+      <c r="L30"/>
+      <c r="M30" t="n">
+        <v>0.000311028706421362</v>
+      </c>
+      <c r="N30"/>
+      <c r="O30" t="n">
+        <v>6.42</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>102</v>
+      </c>
+      <c r="B31" t="s">
+        <v>103</v>
+      </c>
+      <c r="C31"/>
+      <c r="D31" t="n">
+        <v>5</v>
+      </c>
+      <c r="E31" t="n">
+        <v>530.120546377941</v>
+      </c>
+      <c r="F31" t="s">
+        <v>104</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" s="1" t="n">
+        <v>46035</v>
+      </c>
+      <c r="I31"/>
+      <c r="J31" s="1" t="n">
+        <v>46041</v>
+      </c>
+      <c r="K31"/>
+      <c r="L31"/>
+      <c r="M31"/>
+      <c r="N31"/>
+      <c r="O31"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>105</v>
+      </c>
+      <c r="B32" t="s">
+        <v>106</v>
+      </c>
+      <c r="C32"/>
+      <c r="D32" t="n">
+        <v>23</v>
+      </c>
+      <c r="E32" t="n">
+        <v>127.45434</v>
+      </c>
+      <c r="F32" t="s">
+        <v>107</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" s="1" t="n">
+        <v>45518</v>
+      </c>
+      <c r="I32" t="n">
+        <v>32328</v>
+      </c>
+      <c r="J32" s="1" t="n">
+        <v>46041</v>
+      </c>
+      <c r="K32"/>
+      <c r="L32"/>
+      <c r="M32" t="n">
+        <v>0.00394253711952487</v>
+      </c>
+      <c r="N32"/>
+      <c r="O32"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>108</v>
+      </c>
+      <c r="B33" t="s">
+        <v>109</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1.47999</v>
+      </c>
+      <c r="D33" t="n">
+        <v>200</v>
+      </c>
+      <c r="E33" t="n">
+        <v>4.5005</v>
+      </c>
+      <c r="F33" t="s">
+        <v>110</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" s="1" t="n">
+        <v>46027</v>
+      </c>
+      <c r="I33"/>
+      <c r="J33" s="1" t="n">
+        <v>46041</v>
+      </c>
+      <c r="K33"/>
+      <c r="L33"/>
+      <c r="M33"/>
+      <c r="N33"/>
+      <c r="O33" t="n">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>111</v>
+      </c>
+      <c r="B34" t="s">
+        <v>112</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.72786</v>
+      </c>
+      <c r="D34" t="n">
+        <v>500</v>
+      </c>
+      <c r="E34" t="n">
+        <v>2.1878</v>
+      </c>
+      <c r="F34" t="s">
+        <v>113</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" s="1" t="n">
+        <v>45877</v>
+      </c>
+      <c r="I34" t="n">
+        <v>41624</v>
+      </c>
+      <c r="J34" s="1" t="n">
+        <v>46041</v>
+      </c>
+      <c r="K34"/>
+      <c r="L34"/>
+      <c r="M34" t="n">
+        <v>0.0000525610224870267</v>
+      </c>
+      <c r="N34"/>
+      <c r="O34" t="n">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>114</v>
+      </c>
+      <c r="B35" t="s">
+        <v>115</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.94194</v>
+      </c>
+      <c r="D35" t="n">
+        <v>11</v>
+      </c>
+      <c r="E35" t="n">
+        <v>89.96909</v>
+      </c>
+      <c r="F35" t="s">
+        <v>116</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" s="1" t="n">
+        <v>46036</v>
+      </c>
+      <c r="I35"/>
+      <c r="J35" s="1" t="n">
+        <v>46041</v>
+      </c>
+      <c r="K35"/>
+      <c r="L35"/>
+      <c r="M35"/>
+      <c r="N35"/>
+      <c r="O35" t="n">
+        <v>38.57</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>117</v>
+      </c>
+      <c r="B36" t="s">
+        <v>118</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.48873</v>
+      </c>
+      <c r="D36" t="n">
+        <v>110</v>
+      </c>
+      <c r="E36" t="n">
+        <v>5.28836</v>
+      </c>
+      <c r="F36" t="s">
+        <v>119</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" s="1" t="n">
+        <v>45994</v>
+      </c>
+      <c r="I36"/>
+      <c r="J36" s="1" t="n">
+        <v>46041</v>
+      </c>
+      <c r="K36"/>
+      <c r="L36"/>
+      <c r="M36"/>
+      <c r="N36"/>
+      <c r="O36" t="n">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>120</v>
+      </c>
+      <c r="B37" t="s">
+        <v>121</v>
+      </c>
+      <c r="C37" t="n">
+        <v>1.22345</v>
+      </c>
+      <c r="D37" t="n">
+        <v>89</v>
+      </c>
+      <c r="E37" t="n">
+        <v>43.52217</v>
+      </c>
+      <c r="F37" t="s">
+        <v>122</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" s="1" t="n">
+        <v>45384</v>
+      </c>
+      <c r="I37" t="n">
+        <v>34325</v>
+      </c>
+      <c r="J37" s="1" t="n">
+        <v>46041</v>
+      </c>
+      <c r="K37"/>
+      <c r="L37"/>
+      <c r="M37" t="n">
+        <v>0.00126794377276038</v>
+      </c>
+      <c r="N37"/>
+      <c r="O37" t="n">
+        <v>15.76</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>123</v>
+      </c>
+      <c r="B38" t="s">
+        <v>124</v>
+      </c>
+      <c r="C38" t="n">
+        <v>1.30387</v>
+      </c>
+      <c r="D38" t="n">
+        <v>80</v>
+      </c>
+      <c r="E38" t="n">
+        <v>16.20562</v>
+      </c>
+      <c r="F38" t="s">
+        <v>125</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" s="1" t="n">
+        <v>46031</v>
+      </c>
+      <c r="I38"/>
+      <c r="J38" s="1" t="n">
+        <v>46041</v>
+      </c>
+      <c r="K38"/>
+      <c r="L38"/>
+      <c r="M38"/>
+      <c r="N38"/>
+      <c r="O38" t="n">
+        <v>9.42</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>126</v>
+      </c>
+      <c r="B39" t="s">
+        <v>127</v>
+      </c>
+      <c r="C39"/>
+      <c r="D39" t="n">
+        <v>2</v>
+      </c>
+      <c r="E39" t="n">
+        <v>456.930058582329</v>
+      </c>
+      <c r="F39" t="s">
+        <v>128</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" s="1" t="n">
+        <v>46035</v>
+      </c>
+      <c r="I39"/>
+      <c r="J39" s="1" t="n">
+        <v>46041</v>
+      </c>
+      <c r="K39"/>
+      <c r="L39"/>
+      <c r="M39"/>
+      <c r="N39"/>
+      <c r="O39"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>129</v>
+      </c>
+      <c r="B40" t="s">
+        <v>130</v>
+      </c>
+      <c r="C40"/>
+      <c r="D40" t="n">
+        <v>100</v>
+      </c>
+      <c r="E40" t="n">
+        <v>11.222</v>
+      </c>
+      <c r="F40" t="s">
+        <v>131</v>
+      </c>
+      <c r="G40" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" s="1" t="n">
+        <v>46041</v>
+      </c>
+      <c r="I40"/>
+      <c r="J40" s="1" t="n">
+        <v>46041</v>
+      </c>
+      <c r="K40"/>
+      <c r="L40"/>
+      <c r="M40"/>
+      <c r="N40"/>
+      <c r="O40"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>132</v>
+      </c>
+      <c r="B41" t="s">
+        <v>133</v>
+      </c>
+      <c r="C41"/>
+      <c r="D41" t="n">
+        <v>130</v>
+      </c>
+      <c r="E41" t="n">
+        <v>11.94615</v>
+      </c>
+      <c r="F41" t="s">
+        <v>134</v>
+      </c>
+      <c r="G41" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" s="1" t="n">
+        <v>46041</v>
+      </c>
+      <c r="I41"/>
+      <c r="J41" s="1" t="n">
+        <v>46041</v>
+      </c>
+      <c r="K41"/>
+      <c r="L41"/>
+      <c r="M41"/>
+      <c r="N41"/>
+      <c r="O41"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>135</v>
+      </c>
+      <c r="B42" t="s">
+        <v>136</v>
+      </c>
+      <c r="C42"/>
+      <c r="D42" t="n">
+        <v>20</v>
+      </c>
+      <c r="E42" t="n">
+        <v>58.105</v>
+      </c>
+      <c r="F42" t="s">
+        <v>137</v>
+      </c>
+      <c r="G42" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" s="1" t="n">
+        <v>46041</v>
+      </c>
+      <c r="I42"/>
+      <c r="J42" s="1" t="n">
+        <v>46041</v>
+      </c>
+      <c r="K42"/>
+      <c r="L42"/>
+      <c r="M42"/>
+      <c r="N42"/>
+      <c r="O42"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>138</v>
+      </c>
+      <c r="B43" t="s">
+        <v>139</v>
+      </c>
+      <c r="C43"/>
+      <c r="D43" t="n">
+        <v>35</v>
+      </c>
+      <c r="E43" t="n">
+        <v>144.16</v>
+      </c>
+      <c r="F43" t="s">
+        <v>140</v>
+      </c>
+      <c r="G43" t="n">
+        <v>1</v>
+      </c>
+      <c r="H43" s="1" t="n">
+        <v>46041</v>
+      </c>
+      <c r="I43"/>
+      <c r="J43" s="1" t="n">
+        <v>46041</v>
+      </c>
+      <c r="K43"/>
+      <c r="L43"/>
+      <c r="M43"/>
+      <c r="N43"/>
+      <c r="O43"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>141</v>
+      </c>
+      <c r="B44" t="s">
+        <v>142</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1.17727</v>
+      </c>
+      <c r="D44" t="n">
+        <v>270</v>
+      </c>
+      <c r="E44" t="n">
+        <v>3.49051</v>
+      </c>
+      <c r="F44" t="s">
+        <v>143</v>
+      </c>
+      <c r="G44" t="n">
+        <v>1</v>
+      </c>
+      <c r="H44" s="1" t="n">
+        <v>46010</v>
+      </c>
+      <c r="I44"/>
+      <c r="J44" s="1" t="n">
+        <v>46041</v>
+      </c>
+      <c r="K44"/>
+      <c r="L44"/>
+      <c r="M44"/>
+      <c r="N44"/>
+      <c r="O44" t="n">
+        <v>3.22</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>144</v>
+      </c>
+      <c r="B45" t="s">
+        <v>145</v>
+      </c>
+      <c r="C45"/>
+      <c r="D45" t="n">
+        <v>64</v>
+      </c>
+      <c r="E45" t="n">
+        <v>106.35882</v>
+      </c>
+      <c r="F45" t="s">
+        <v>146</v>
+      </c>
+      <c r="G45" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45" s="1" t="n">
+        <v>46041</v>
+      </c>
+      <c r="I45"/>
+      <c r="J45" s="1" t="n">
+        <v>46041</v>
+      </c>
+      <c r="K45"/>
+      <c r="L45"/>
+      <c r="M45"/>
+      <c r="N45"/>
+      <c r="O45"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>147</v>
+      </c>
+      <c r="B46" t="s">
+        <v>148</v>
+      </c>
+      <c r="C46"/>
+      <c r="D46" t="n">
+        <v>131</v>
+      </c>
+      <c r="E46" t="n">
+        <v>7.652</v>
+      </c>
+      <c r="F46" t="s">
+        <v>149</v>
+      </c>
+      <c r="G46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" s="1" t="n">
+        <v>46041</v>
+      </c>
+      <c r="I46"/>
+      <c r="J46" s="1" t="n">
+        <v>46041</v>
+      </c>
+      <c r="K46"/>
+      <c r="L46"/>
+      <c r="M46"/>
+      <c r="N46"/>
+      <c r="O46"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>150</v>
+      </c>
+      <c r="B47" t="s">
+        <v>151</v>
+      </c>
+      <c r="C47"/>
+      <c r="D47" t="n">
+        <v>470</v>
+      </c>
+      <c r="E47" t="n">
+        <v>5.333</v>
+      </c>
+      <c r="F47" t="s">
+        <v>152</v>
+      </c>
+      <c r="G47" t="n">
+        <v>1</v>
+      </c>
+      <c r="H47" s="1" t="n">
+        <v>46041</v>
+      </c>
+      <c r="I47"/>
+      <c r="J47" s="1" t="n">
+        <v>46041</v>
+      </c>
+      <c r="K47"/>
+      <c r="L47"/>
+      <c r="M47"/>
+      <c r="N47"/>
+      <c r="O47"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>153</v>
+      </c>
+      <c r="B48" t="s">
+        <v>154</v>
+      </c>
+      <c r="C48"/>
+      <c r="D48" t="n">
+        <v>15</v>
+      </c>
+      <c r="E48" t="n">
+        <v>68.59</v>
+      </c>
+      <c r="F48" t="s">
+        <v>155</v>
+      </c>
+      <c r="G48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H48" s="1" t="n">
+        <v>46041</v>
+      </c>
+      <c r="I48"/>
+      <c r="J48" s="1" t="n">
+        <v>46041</v>
+      </c>
+      <c r="K48"/>
+      <c r="L48"/>
+      <c r="M48"/>
+      <c r="N48"/>
+      <c r="O48"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>156</v>
+      </c>
+      <c r="B49" t="s">
+        <v>157</v>
+      </c>
+      <c r="C49"/>
+      <c r="D49" t="n">
+        <v>10</v>
+      </c>
+      <c r="E49" t="n">
+        <v>115.065</v>
+      </c>
+      <c r="F49" t="s">
+        <v>158</v>
+      </c>
+      <c r="G49" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49" s="1" t="n">
+        <v>46041</v>
+      </c>
+      <c r="I49"/>
+      <c r="J49" s="1" t="n">
+        <v>46041</v>
+      </c>
+      <c r="K49"/>
+      <c r="L49"/>
+      <c r="M49"/>
+      <c r="N49"/>
+      <c r="O49"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
